--- a/first_tapeout_gps/Schedule/wbs.xlsx
+++ b/first_tapeout_gps/Schedule/wbs.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8E6F2E-6A87-7F43-9F4A-EEC460284BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA86612D-BAF5-5F49-B41C-B8D75C635873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4100" yWindow="-21100" windowWidth="38400" windowHeight="19580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4100" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクトのスケジュール" sheetId="11" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="75">
   <si>
     <t>このワークシートでプロジェクトのスケジュール​​を作成します。
 セル B1 には、このプロジェクトのタイトルを入力します。
@@ -532,6 +532,22 @@
     <t>福岡・西尾</t>
     <rPh sb="0" eb="2">
       <t xml:space="preserve">フクオカ </t>
+    </rPh>
+    <phoneticPr fontId="29"/>
+  </si>
+  <si>
+    <t>仮合成と回路規模の確認</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">カリゴウセイ </t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t xml:space="preserve">カイロ </t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">キボ </t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t xml:space="preserve">カクニｎ </t>
     </rPh>
     <phoneticPr fontId="29"/>
   </si>
@@ -548,7 +564,7 @@
     <numFmt numFmtId="178" formatCode="m/d/yy;@"/>
     <numFmt numFmtId="179" formatCode="aaa\,\ yyyy/m/d"/>
     <numFmt numFmtId="180" formatCode="d"/>
-    <numFmt numFmtId="185" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="181" formatCode="yyyy/m/d;@"/>
   </numFmts>
   <fonts count="40">
     <font>
@@ -1349,7 +1365,7 @@
     <xf numFmtId="0" fontId="1" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1576,74 +1592,68 @@
     <xf numFmtId="0" fontId="17" fillId="45" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="181" fontId="1" fillId="3" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="45" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="25" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="4" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="25" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="11" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="25" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="10" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="46" borderId="2" xfId="12" applyFill="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="46" borderId="2" xfId="11" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="25" fillId="46" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="46" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
       <alignment horizontal="right" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
       <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="12" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="185" fontId="1" fillId="3" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="1" fillId="45" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="25" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="1" fillId="4" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="25" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="1" fillId="11" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="25" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="1" fillId="10" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="46" borderId="2" xfId="12" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="46" borderId="2" xfId="11" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="25" fillId="46" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="1" fillId="46" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="46" borderId="2" xfId="12" applyFill="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2252,7 +2262,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BL43"/>
+  <dimension ref="A1:BL44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.5703125" style="8" customWidth="1"/>
@@ -2302,106 +2312,106 @@
       <c r="B3" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="82" t="s">
+      <c r="C3" s="101" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="83"/>
-      <c r="E3" s="87">
+      <c r="D3" s="102"/>
+      <c r="E3" s="100">
         <v>46219</v>
       </c>
-      <c r="F3" s="87"/>
+      <c r="F3" s="100"/>
     </row>
     <row r="4" spans="1:64" ht="30" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="82" t="s">
+      <c r="C4" s="101" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="83"/>
+      <c r="D4" s="102"/>
       <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="I4" s="84">
+      <c r="I4" s="97">
         <f>I5</f>
         <v>46216</v>
       </c>
-      <c r="J4" s="85"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="85"/>
-      <c r="M4" s="85"/>
-      <c r="N4" s="85"/>
-      <c r="O4" s="86"/>
-      <c r="P4" s="84">
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="97">
         <f>P5</f>
         <v>46223</v>
       </c>
-      <c r="Q4" s="85"/>
-      <c r="R4" s="85"/>
-      <c r="S4" s="85"/>
-      <c r="T4" s="85"/>
-      <c r="U4" s="85"/>
-      <c r="V4" s="86"/>
-      <c r="W4" s="84">
+      <c r="Q4" s="98"/>
+      <c r="R4" s="98"/>
+      <c r="S4" s="98"/>
+      <c r="T4" s="98"/>
+      <c r="U4" s="98"/>
+      <c r="V4" s="99"/>
+      <c r="W4" s="97">
         <f>W5</f>
         <v>46230</v>
       </c>
-      <c r="X4" s="85"/>
-      <c r="Y4" s="85"/>
-      <c r="Z4" s="85"/>
-      <c r="AA4" s="85"/>
-      <c r="AB4" s="85"/>
-      <c r="AC4" s="86"/>
-      <c r="AD4" s="84">
+      <c r="X4" s="98"/>
+      <c r="Y4" s="98"/>
+      <c r="Z4" s="98"/>
+      <c r="AA4" s="98"/>
+      <c r="AB4" s="98"/>
+      <c r="AC4" s="99"/>
+      <c r="AD4" s="97">
         <f>AD5</f>
         <v>46237</v>
       </c>
-      <c r="AE4" s="85"/>
-      <c r="AF4" s="85"/>
-      <c r="AG4" s="85"/>
-      <c r="AH4" s="85"/>
-      <c r="AI4" s="85"/>
-      <c r="AJ4" s="86"/>
-      <c r="AK4" s="84">
+      <c r="AE4" s="98"/>
+      <c r="AF4" s="98"/>
+      <c r="AG4" s="98"/>
+      <c r="AH4" s="98"/>
+      <c r="AI4" s="98"/>
+      <c r="AJ4" s="99"/>
+      <c r="AK4" s="97">
         <f>AK5</f>
         <v>46244</v>
       </c>
-      <c r="AL4" s="85"/>
-      <c r="AM4" s="85"/>
-      <c r="AN4" s="85"/>
-      <c r="AO4" s="85"/>
-      <c r="AP4" s="85"/>
-      <c r="AQ4" s="86"/>
-      <c r="AR4" s="84">
+      <c r="AL4" s="98"/>
+      <c r="AM4" s="98"/>
+      <c r="AN4" s="98"/>
+      <c r="AO4" s="98"/>
+      <c r="AP4" s="98"/>
+      <c r="AQ4" s="99"/>
+      <c r="AR4" s="97">
         <f>AR5</f>
         <v>46251</v>
       </c>
-      <c r="AS4" s="85"/>
-      <c r="AT4" s="85"/>
-      <c r="AU4" s="85"/>
-      <c r="AV4" s="85"/>
-      <c r="AW4" s="85"/>
-      <c r="AX4" s="86"/>
-      <c r="AY4" s="84">
+      <c r="AS4" s="98"/>
+      <c r="AT4" s="98"/>
+      <c r="AU4" s="98"/>
+      <c r="AV4" s="98"/>
+      <c r="AW4" s="98"/>
+      <c r="AX4" s="99"/>
+      <c r="AY4" s="97">
         <f>AY5</f>
         <v>46258</v>
       </c>
-      <c r="AZ4" s="85"/>
-      <c r="BA4" s="85"/>
-      <c r="BB4" s="85"/>
-      <c r="BC4" s="85"/>
-      <c r="BD4" s="85"/>
-      <c r="BE4" s="86"/>
-      <c r="BF4" s="84">
+      <c r="AZ4" s="98"/>
+      <c r="BA4" s="98"/>
+      <c r="BB4" s="98"/>
+      <c r="BC4" s="98"/>
+      <c r="BD4" s="98"/>
+      <c r="BE4" s="99"/>
+      <c r="BF4" s="97">
         <f>BF5</f>
         <v>46265</v>
       </c>
-      <c r="BG4" s="85"/>
-      <c r="BH4" s="85"/>
-      <c r="BI4" s="85"/>
-      <c r="BJ4" s="85"/>
-      <c r="BK4" s="85"/>
-      <c r="BL4" s="86"/>
+      <c r="BG4" s="98"/>
+      <c r="BH4" s="98"/>
+      <c r="BI4" s="98"/>
+      <c r="BJ4" s="98"/>
+      <c r="BK4" s="98"/>
+      <c r="BL4" s="99"/>
     </row>
     <row r="5" spans="1:64" ht="15" customHeight="1">
       <c r="A5" s="9" t="s">
@@ -2618,7 +2628,7 @@
         <v>46266</v>
       </c>
       <c r="BH5" s="77">
-        <f t="shared" ref="BH5:BN5" si="2">BG5+1</f>
+        <f t="shared" ref="BH5:BL5" si="2">BG5+1</f>
         <v>46267</v>
       </c>
       <c r="BI5" s="77">
@@ -2966,7 +2976,7 @@
       <c r="F8" s="72"/>
       <c r="G8" s="40"/>
       <c r="H8" s="40" t="str">
-        <f t="shared" ref="H8:H40" si="5">IF(OR(ISBLANK(タスク_開始),ISBLANK(タスク_終了)),"",タスク_終了-タスク_開始+1)</f>
+        <f t="shared" ref="H8:H41" si="5">IF(OR(ISBLANK(タスク_開始),ISBLANK(タスク_終了)),"",タスク_終了-タスク_開始+1)</f>
         <v/>
       </c>
       <c r="I8" s="5"/>
@@ -3039,11 +3049,11 @@
       <c r="D9" s="41">
         <v>1</v>
       </c>
-      <c r="E9" s="89">
+      <c r="E9" s="82">
         <f>プロジェクトの開始</f>
         <v>46219</v>
       </c>
-      <c r="F9" s="89">
+      <c r="F9" s="82">
         <v>46229</v>
       </c>
       <c r="G9" s="40"/>
@@ -3119,12 +3129,12 @@
         <v>63</v>
       </c>
       <c r="D10" s="41">
-        <v>0</v>
-      </c>
-      <c r="E10" s="89">
+        <v>0.75</v>
+      </c>
+      <c r="E10" s="82">
         <v>46230</v>
       </c>
-      <c r="F10" s="89">
+      <c r="F10" s="82">
         <v>46236</v>
       </c>
       <c r="G10" s="40"/>
@@ -3200,11 +3210,11 @@
       <c r="D11" s="41">
         <v>0</v>
       </c>
-      <c r="E11" s="89">
+      <c r="E11" s="82">
         <f>F10</f>
         <v>46236</v>
       </c>
-      <c r="F11" s="89">
+      <c r="F11" s="82">
         <v>46242</v>
       </c>
       <c r="G11" s="40"/>
@@ -3271,7 +3281,7 @@
     </row>
     <row r="12" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A12" s="8"/>
-      <c r="B12" s="88" t="s">
+      <c r="B12" s="23" t="s">
         <v>51</v>
       </c>
       <c r="C12" s="15" t="s">
@@ -3280,10 +3290,10 @@
       <c r="D12" s="41">
         <v>0</v>
       </c>
-      <c r="E12" s="89">
+      <c r="E12" s="82">
         <v>46235</v>
       </c>
-      <c r="F12" s="89">
+      <c r="F12" s="82">
         <v>46263</v>
       </c>
       <c r="G12" s="40"/>
@@ -3355,8 +3365,8 @@
       </c>
       <c r="C13" s="79"/>
       <c r="D13" s="80"/>
-      <c r="E13" s="90"/>
-      <c r="F13" s="90"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
       <c r="G13" s="40"/>
       <c r="H13" s="40"/>
       <c r="I13" s="5"/>
@@ -3418,19 +3428,19 @@
     </row>
     <row r="14" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A14" s="8"/>
-      <c r="B14" s="100" t="s">
+      <c r="B14" s="93" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="101" t="s">
+      <c r="C14" s="94" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="102">
+      <c r="D14" s="95">
         <v>0</v>
       </c>
-      <c r="E14" s="103">
+      <c r="E14" s="96">
         <v>46243</v>
       </c>
-      <c r="F14" s="103">
+      <c r="F14" s="96">
         <v>46251</v>
       </c>
       <c r="G14" s="40"/>
@@ -3494,19 +3504,19 @@
     </row>
     <row r="15" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A15" s="8"/>
-      <c r="B15" s="104" t="s">
+      <c r="B15" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="101" t="s">
+      <c r="C15" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="102">
+      <c r="D15" s="95">
         <v>0</v>
       </c>
-      <c r="E15" s="103">
+      <c r="E15" s="96">
         <v>46243</v>
       </c>
-      <c r="F15" s="103">
+      <c r="F15" s="96">
         <v>46258</v>
       </c>
       <c r="G15" s="40"/>
@@ -3570,19 +3580,19 @@
     </row>
     <row r="16" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A16" s="8"/>
-      <c r="B16" s="104" t="s">
+      <c r="B16" s="93" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="101" t="s">
+      <c r="C16" s="94" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="102">
+      <c r="D16" s="95">
         <v>0</v>
       </c>
-      <c r="E16" s="103">
+      <c r="E16" s="96">
         <v>46258</v>
       </c>
-      <c r="F16" s="103">
+      <c r="F16" s="96">
         <v>46261</v>
       </c>
       <c r="G16" s="40"/>
@@ -3646,19 +3656,19 @@
     </row>
     <row r="17" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A17" s="8"/>
-      <c r="B17" s="104" t="s">
+      <c r="B17" s="93" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="101" t="s">
+      <c r="C17" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="102">
+      <c r="D17" s="95">
         <v>0</v>
       </c>
-      <c r="E17" s="103">
+      <c r="E17" s="96">
         <v>46261</v>
       </c>
-      <c r="F17" s="103">
+      <c r="F17" s="96">
         <v>46263</v>
       </c>
       <c r="G17" s="40"/>
@@ -3722,19 +3732,19 @@
     </row>
     <row r="18" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A18" s="8"/>
-      <c r="B18" s="104" t="s">
+      <c r="B18" s="93" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="101" t="s">
+      <c r="C18" s="94" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="102">
+      <c r="D18" s="95">
         <v>0</v>
       </c>
-      <c r="E18" s="103">
+      <c r="E18" s="96">
         <v>46264</v>
       </c>
-      <c r="F18" s="103">
+      <c r="F18" s="96">
         <v>46266</v>
       </c>
       <c r="G18" s="40"/>
@@ -3805,8 +3815,8 @@
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="43"/>
-      <c r="E19" s="91"/>
-      <c r="F19" s="92"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="85"/>
       <c r="G19" s="40"/>
       <c r="H19" s="40" t="str">
         <f t="shared" si="5"/>
@@ -3880,10 +3890,10 @@
       <c r="D20" s="44">
         <v>0</v>
       </c>
-      <c r="E20" s="93">
+      <c r="E20" s="86">
         <v>46267</v>
       </c>
-      <c r="F20" s="93">
+      <c r="F20" s="86">
         <v>46270</v>
       </c>
       <c r="G20" s="40"/>
@@ -3959,10 +3969,10 @@
       <c r="D21" s="44">
         <v>0</v>
       </c>
-      <c r="E21" s="93">
+      <c r="E21" s="86">
         <v>46271</v>
       </c>
-      <c r="F21" s="93">
+      <c r="F21" s="86">
         <v>46277</v>
       </c>
       <c r="G21" s="40"/>
@@ -4038,10 +4048,10 @@
       <c r="D22" s="44">
         <v>0</v>
       </c>
-      <c r="E22" s="93">
+      <c r="E22" s="86">
         <v>46278</v>
       </c>
-      <c r="F22" s="93">
+      <c r="F22" s="86">
         <v>46282</v>
       </c>
       <c r="G22" s="40"/>
@@ -4117,10 +4127,10 @@
       <c r="D23" s="44">
         <v>0</v>
       </c>
-      <c r="E23" s="93">
+      <c r="E23" s="86">
         <v>46283</v>
       </c>
-      <c r="F23" s="93">
+      <c r="F23" s="86">
         <v>46286</v>
       </c>
       <c r="G23" s="40"/>
@@ -4196,10 +4206,10 @@
       <c r="D24" s="44">
         <v>0</v>
       </c>
-      <c r="E24" s="93">
+      <c r="E24" s="86">
         <v>46272</v>
       </c>
-      <c r="F24" s="93">
+      <c r="F24" s="86">
         <v>46286</v>
       </c>
       <c r="G24" s="40"/>
@@ -4262,21 +4272,24 @@
       <c r="BL24" s="5"/>
     </row>
     <row r="25" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A25" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="94"/>
-      <c r="F25" s="95"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="44">
+        <v>0</v>
+      </c>
+      <c r="E25" s="86">
+        <v>46287</v>
+      </c>
+      <c r="F25" s="86">
+        <v>46290</v>
+      </c>
       <c r="G25" s="40"/>
-      <c r="H25" s="40" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="H25" s="40"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
@@ -4293,7 +4306,7 @@
       <c r="V25" s="5"/>
       <c r="W25" s="5"/>
       <c r="X25" s="5"/>
-      <c r="Y25" s="5"/>
+      <c r="Y25" s="6"/>
       <c r="Z25" s="5"/>
       <c r="AA25" s="5"/>
       <c r="AB25" s="5"/>
@@ -4335,26 +4348,20 @@
       <c r="BL25" s="5"/>
     </row>
     <row r="26" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A26" s="8"/>
-      <c r="B26" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="D26" s="47">
-        <v>0</v>
-      </c>
-      <c r="E26" s="96">
-        <v>46287</v>
-      </c>
-      <c r="F26" s="96">
-        <v>46292</v>
-      </c>
+      <c r="A26" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="88"/>
       <c r="G26" s="40"/>
-      <c r="H26" s="40">
+      <c r="H26" s="40" t="str">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v/>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
@@ -4416,19 +4423,19 @@
     <row r="27" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A27" s="8"/>
       <c r="B27" s="25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D27" s="47">
         <v>0</v>
       </c>
-      <c r="E27" s="96">
-        <v>46293</v>
-      </c>
-      <c r="F27" s="96">
-        <v>46298</v>
+      <c r="E27" s="89">
+        <v>46287</v>
+      </c>
+      <c r="F27" s="89">
+        <v>46292</v>
       </c>
       <c r="G27" s="40"/>
       <c r="H27" s="40">
@@ -4495,24 +4502,24 @@
     <row r="28" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A28" s="8"/>
       <c r="B28" s="25" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D28" s="47">
         <v>0</v>
       </c>
-      <c r="E28" s="96">
-        <v>46299</v>
-      </c>
-      <c r="F28" s="96">
-        <v>46302</v>
+      <c r="E28" s="89">
+        <v>46293</v>
+      </c>
+      <c r="F28" s="89">
+        <v>46298</v>
       </c>
       <c r="G28" s="40"/>
       <c r="H28" s="40">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
@@ -4572,20 +4579,26 @@
       <c r="BL28" s="5"/>
     </row>
     <row r="29" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A29" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B29" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" s="20"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="97"/>
-      <c r="F29" s="98"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="47">
+        <v>0</v>
+      </c>
+      <c r="E29" s="89">
+        <v>46299</v>
+      </c>
+      <c r="F29" s="89">
+        <v>46302</v>
+      </c>
       <c r="G29" s="40"/>
-      <c r="H29" s="40" t="str">
+      <c r="H29" s="40">
         <f t="shared" si="5"/>
-        <v/>
+        <v>4</v>
       </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
@@ -4645,26 +4658,20 @@
       <c r="BL29" s="5"/>
     </row>
     <row r="30" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A30" s="8"/>
-      <c r="B30" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" s="50">
-        <v>0</v>
-      </c>
-      <c r="E30" s="99">
-        <v>46303</v>
-      </c>
-      <c r="F30" s="99">
-        <v>46315</v>
-      </c>
+      <c r="A30" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="20"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="90"/>
+      <c r="F30" s="91"/>
       <c r="G30" s="40"/>
-      <c r="H30" s="40">
+      <c r="H30" s="40" t="str">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v/>
       </c>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
@@ -4726,7 +4733,7 @@
     <row r="31" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A31" s="8"/>
       <c r="B31" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>62</v>
@@ -4734,10 +4741,10 @@
       <c r="D31" s="50">
         <v>0</v>
       </c>
-      <c r="E31" s="99">
+      <c r="E31" s="92">
         <v>46303</v>
       </c>
-      <c r="F31" s="99">
+      <c r="F31" s="92">
         <v>46315</v>
       </c>
       <c r="G31" s="40"/>
@@ -4805,24 +4812,24 @@
     <row r="32" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A32" s="8"/>
       <c r="B32" s="26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D32" s="50">
         <v>0</v>
       </c>
-      <c r="E32" s="99">
-        <v>46275</v>
-      </c>
-      <c r="F32" s="99">
+      <c r="E32" s="92">
+        <v>46303</v>
+      </c>
+      <c r="F32" s="92">
         <v>46315</v>
       </c>
       <c r="G32" s="40"/>
       <c r="H32" s="40">
         <f t="shared" si="5"/>
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
@@ -4884,24 +4891,24 @@
     <row r="33" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A33" s="8"/>
       <c r="B33" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D33" s="50">
         <v>0</v>
       </c>
-      <c r="E33" s="99">
-        <v>46316</v>
-      </c>
-      <c r="F33" s="99">
-        <v>46331</v>
+      <c r="E33" s="92">
+        <v>46275</v>
+      </c>
+      <c r="F33" s="92">
+        <v>46315</v>
       </c>
       <c r="G33" s="40"/>
       <c r="H33" s="40">
         <f t="shared" si="5"/>
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
@@ -4961,18 +4968,26 @@
       <c r="BL33" s="5"/>
     </row>
     <row r="34" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A34" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B34" s="27"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="73"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="50">
+        <v>0</v>
+      </c>
+      <c r="E34" s="92">
+        <v>46316</v>
+      </c>
+      <c r="F34" s="92">
+        <v>46331</v>
+      </c>
       <c r="G34" s="40"/>
-      <c r="H34" s="40" t="str">
+      <c r="H34" s="40">
         <f t="shared" si="5"/>
-        <v/>
+        <v>16</v>
       </c>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
@@ -5032,14 +5047,19 @@
       <c r="BL34" s="5"/>
     </row>
     <row r="35" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A35" s="8"/>
+      <c r="A35" s="8" t="s">
+        <v>21</v>
+      </c>
       <c r="B35" s="27"/>
       <c r="C35" s="22"/>
       <c r="D35" s="51"/>
       <c r="E35" s="73"/>
       <c r="F35" s="73"/>
       <c r="G35" s="40"/>
-      <c r="H35" s="40"/>
+      <c r="H35" s="40" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
@@ -5362,104 +5382,170 @@
       <c r="BL39" s="5"/>
     </row>
     <row r="40" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="8"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="73"/>
+      <c r="F40" s="73"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="5"/>
+      <c r="T40" s="5"/>
+      <c r="U40" s="5"/>
+      <c r="V40" s="5"/>
+      <c r="W40" s="5"/>
+      <c r="X40" s="5"/>
+      <c r="Y40" s="5"/>
+      <c r="Z40" s="5"/>
+      <c r="AA40" s="5"/>
+      <c r="AB40" s="5"/>
+      <c r="AC40" s="5"/>
+      <c r="AD40" s="5"/>
+      <c r="AE40" s="5"/>
+      <c r="AF40" s="5"/>
+      <c r="AG40" s="5"/>
+      <c r="AH40" s="5"/>
+      <c r="AI40" s="5"/>
+      <c r="AJ40" s="5"/>
+      <c r="AK40" s="5"/>
+      <c r="AL40" s="5"/>
+      <c r="AM40" s="5"/>
+      <c r="AN40" s="5"/>
+      <c r="AO40" s="5"/>
+      <c r="AP40" s="5"/>
+      <c r="AQ40" s="5"/>
+      <c r="AR40" s="5"/>
+      <c r="AS40" s="5"/>
+      <c r="AT40" s="5"/>
+      <c r="AU40" s="5"/>
+      <c r="AV40" s="5"/>
+      <c r="AW40" s="5"/>
+      <c r="AX40" s="5"/>
+      <c r="AY40" s="5"/>
+      <c r="AZ40" s="5"/>
+      <c r="BA40" s="5"/>
+      <c r="BB40" s="5"/>
+      <c r="BC40" s="5"/>
+      <c r="BD40" s="5"/>
+      <c r="BE40" s="5"/>
+      <c r="BF40" s="5"/>
+      <c r="BG40" s="5"/>
+      <c r="BH40" s="5"/>
+      <c r="BI40" s="5"/>
+      <c r="BJ40" s="5"/>
+      <c r="BK40" s="5"/>
+      <c r="BL40" s="5"/>
+    </row>
+    <row r="41" spans="1:64" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
+      <c r="A41" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="52" t="s">
+      <c r="B41" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="53"/>
-      <c r="D40" s="54"/>
-      <c r="E40" s="74"/>
-      <c r="F40" s="75"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="55" t="str">
+      <c r="C41" s="53"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="74"/>
+      <c r="F41" s="75"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="55" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
-      <c r="N40" s="7"/>
-      <c r="O40" s="7"/>
-      <c r="P40" s="7"/>
-      <c r="Q40" s="7"/>
-      <c r="R40" s="7"/>
-      <c r="S40" s="7"/>
-      <c r="T40" s="7"/>
-      <c r="U40" s="7"/>
-      <c r="V40" s="7"/>
-      <c r="W40" s="7"/>
-      <c r="X40" s="7"/>
-      <c r="Y40" s="7"/>
-      <c r="Z40" s="7"/>
-      <c r="AA40" s="7"/>
-      <c r="AB40" s="7"/>
-      <c r="AC40" s="7"/>
-      <c r="AD40" s="7"/>
-      <c r="AE40" s="7"/>
-      <c r="AF40" s="7"/>
-      <c r="AG40" s="7"/>
-      <c r="AH40" s="7"/>
-      <c r="AI40" s="7"/>
-      <c r="AJ40" s="7"/>
-      <c r="AK40" s="7"/>
-      <c r="AL40" s="7"/>
-      <c r="AM40" s="7"/>
-      <c r="AN40" s="7"/>
-      <c r="AO40" s="7"/>
-      <c r="AP40" s="7"/>
-      <c r="AQ40" s="7"/>
-      <c r="AR40" s="7"/>
-      <c r="AS40" s="7"/>
-      <c r="AT40" s="7"/>
-      <c r="AU40" s="7"/>
-      <c r="AV40" s="7"/>
-      <c r="AW40" s="7"/>
-      <c r="AX40" s="7"/>
-      <c r="AY40" s="7"/>
-      <c r="AZ40" s="7"/>
-      <c r="BA40" s="7"/>
-      <c r="BB40" s="7"/>
-      <c r="BC40" s="7"/>
-      <c r="BD40" s="7"/>
-      <c r="BE40" s="7"/>
-      <c r="BF40" s="7"/>
-      <c r="BG40" s="7"/>
-      <c r="BH40" s="7"/>
-      <c r="BI40" s="7"/>
-      <c r="BJ40" s="7"/>
-      <c r="BK40" s="7"/>
-      <c r="BL40" s="7"/>
-    </row>
-    <row r="41" spans="1:64" ht="30" customHeight="1">
-      <c r="G41" s="3"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="7"/>
+      <c r="N41" s="7"/>
+      <c r="O41" s="7"/>
+      <c r="P41" s="7"/>
+      <c r="Q41" s="7"/>
+      <c r="R41" s="7"/>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+      <c r="U41" s="7"/>
+      <c r="V41" s="7"/>
+      <c r="W41" s="7"/>
+      <c r="X41" s="7"/>
+      <c r="Y41" s="7"/>
+      <c r="Z41" s="7"/>
+      <c r="AA41" s="7"/>
+      <c r="AB41" s="7"/>
+      <c r="AC41" s="7"/>
+      <c r="AD41" s="7"/>
+      <c r="AE41" s="7"/>
+      <c r="AF41" s="7"/>
+      <c r="AG41" s="7"/>
+      <c r="AH41" s="7"/>
+      <c r="AI41" s="7"/>
+      <c r="AJ41" s="7"/>
+      <c r="AK41" s="7"/>
+      <c r="AL41" s="7"/>
+      <c r="AM41" s="7"/>
+      <c r="AN41" s="7"/>
+      <c r="AO41" s="7"/>
+      <c r="AP41" s="7"/>
+      <c r="AQ41" s="7"/>
+      <c r="AR41" s="7"/>
+      <c r="AS41" s="7"/>
+      <c r="AT41" s="7"/>
+      <c r="AU41" s="7"/>
+      <c r="AV41" s="7"/>
+      <c r="AW41" s="7"/>
+      <c r="AX41" s="7"/>
+      <c r="AY41" s="7"/>
+      <c r="AZ41" s="7"/>
+      <c r="BA41" s="7"/>
+      <c r="BB41" s="7"/>
+      <c r="BC41" s="7"/>
+      <c r="BD41" s="7"/>
+      <c r="BE41" s="7"/>
+      <c r="BF41" s="7"/>
+      <c r="BG41" s="7"/>
+      <c r="BH41" s="7"/>
+      <c r="BI41" s="7"/>
+      <c r="BJ41" s="7"/>
+      <c r="BK41" s="7"/>
+      <c r="BL41" s="7"/>
     </row>
     <row r="42" spans="1:64" ht="30" customHeight="1">
-      <c r="C42" s="56"/>
-      <c r="F42" s="57"/>
+      <c r="G42" s="3"/>
     </row>
     <row r="43" spans="1:64" ht="30" customHeight="1">
-      <c r="C43" s="58"/>
+      <c r="C43" s="56"/>
+      <c r="F43" s="57"/>
+    </row>
+    <row r="44" spans="1:64" ht="30" customHeight="1">
+      <c r="C44" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
   </mergeCells>
   <phoneticPr fontId="29"/>
-  <conditionalFormatting sqref="D7:D40">
+  <conditionalFormatting sqref="D7:D41">
     <cfRule type="dataBar" priority="14">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -5473,12 +5559,12 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:BL40">
+  <conditionalFormatting sqref="I5:BL41">
     <cfRule type="expression" dxfId="2" priority="33">
       <formula>AND(TODAY()&gt;=I$5,TODAY()&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:BL40">
+  <conditionalFormatting sqref="I7:BL41">
     <cfRule type="expression" dxfId="1" priority="27">
       <formula>AND(タスク_開始&lt;=I$5,ROUNDDOWN((タスク_終了-タスク_開始+1)*タスク_進捗状況,0)+タスク_開始-1&gt;=I$5)</formula>
     </cfRule>
@@ -5502,7 +5588,7 @@
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="39" max="16383" man="1"/>
+    <brk id="40" max="16383" man="1"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="1" max="1048575" man="1"/>
@@ -5523,7 +5609,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D7:D40</xm:sqref>
+          <xm:sqref>D7:D41</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -5656,15 +5742,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5952,6 +6029,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5144944C-1F1D-4162-962A-96F3FC8455D8}">
   <ds:schemaRefs>
@@ -5965,14 +6051,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{708DBB9E-6D89-4A94-9DC5-964B7833E11C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5991,4 +6069,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/first_tapeout_gps/Schedule/wbs.xlsx
+++ b/first_tapeout_gps/Schedule/wbs.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA86612D-BAF5-5F49-B41C-B8D75C635873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5854DAC3-28AB-6449-A4F6-F13BE0485408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4100" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクトのスケジュール" sheetId="11" r:id="rId1"/>
@@ -1637,6 +1637,12 @@
     <xf numFmtId="181" fontId="1" fillId="46" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1648,12 +1654,6 @@
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2312,106 +2312,106 @@
       <c r="B3" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="101" t="s">
+      <c r="C3" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="102"/>
-      <c r="E3" s="100">
+      <c r="D3" s="98"/>
+      <c r="E3" s="102">
         <v>46219</v>
       </c>
-      <c r="F3" s="100"/>
+      <c r="F3" s="102"/>
     </row>
     <row r="4" spans="1:64" ht="30" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="101" t="s">
+      <c r="C4" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="102"/>
+      <c r="D4" s="98"/>
       <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="I4" s="97">
+      <c r="I4" s="99">
         <f>I5</f>
         <v>46216</v>
       </c>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="97">
+      <c r="J4" s="100"/>
+      <c r="K4" s="100"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="100"/>
+      <c r="N4" s="100"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="99">
         <f>P5</f>
         <v>46223</v>
       </c>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="98"/>
-      <c r="S4" s="98"/>
-      <c r="T4" s="98"/>
-      <c r="U4" s="98"/>
-      <c r="V4" s="99"/>
-      <c r="W4" s="97">
+      <c r="Q4" s="100"/>
+      <c r="R4" s="100"/>
+      <c r="S4" s="100"/>
+      <c r="T4" s="100"/>
+      <c r="U4" s="100"/>
+      <c r="V4" s="101"/>
+      <c r="W4" s="99">
         <f>W5</f>
         <v>46230</v>
       </c>
-      <c r="X4" s="98"/>
-      <c r="Y4" s="98"/>
-      <c r="Z4" s="98"/>
-      <c r="AA4" s="98"/>
-      <c r="AB4" s="98"/>
-      <c r="AC4" s="99"/>
-      <c r="AD4" s="97">
+      <c r="X4" s="100"/>
+      <c r="Y4" s="100"/>
+      <c r="Z4" s="100"/>
+      <c r="AA4" s="100"/>
+      <c r="AB4" s="100"/>
+      <c r="AC4" s="101"/>
+      <c r="AD4" s="99">
         <f>AD5</f>
         <v>46237</v>
       </c>
-      <c r="AE4" s="98"/>
-      <c r="AF4" s="98"/>
-      <c r="AG4" s="98"/>
-      <c r="AH4" s="98"/>
-      <c r="AI4" s="98"/>
-      <c r="AJ4" s="99"/>
-      <c r="AK4" s="97">
+      <c r="AE4" s="100"/>
+      <c r="AF4" s="100"/>
+      <c r="AG4" s="100"/>
+      <c r="AH4" s="100"/>
+      <c r="AI4" s="100"/>
+      <c r="AJ4" s="101"/>
+      <c r="AK4" s="99">
         <f>AK5</f>
         <v>46244</v>
       </c>
-      <c r="AL4" s="98"/>
-      <c r="AM4" s="98"/>
-      <c r="AN4" s="98"/>
-      <c r="AO4" s="98"/>
-      <c r="AP4" s="98"/>
-      <c r="AQ4" s="99"/>
-      <c r="AR4" s="97">
+      <c r="AL4" s="100"/>
+      <c r="AM4" s="100"/>
+      <c r="AN4" s="100"/>
+      <c r="AO4" s="100"/>
+      <c r="AP4" s="100"/>
+      <c r="AQ4" s="101"/>
+      <c r="AR4" s="99">
         <f>AR5</f>
         <v>46251</v>
       </c>
-      <c r="AS4" s="98"/>
-      <c r="AT4" s="98"/>
-      <c r="AU4" s="98"/>
-      <c r="AV4" s="98"/>
-      <c r="AW4" s="98"/>
-      <c r="AX4" s="99"/>
-      <c r="AY4" s="97">
+      <c r="AS4" s="100"/>
+      <c r="AT4" s="100"/>
+      <c r="AU4" s="100"/>
+      <c r="AV4" s="100"/>
+      <c r="AW4" s="100"/>
+      <c r="AX4" s="101"/>
+      <c r="AY4" s="99">
         <f>AY5</f>
         <v>46258</v>
       </c>
-      <c r="AZ4" s="98"/>
-      <c r="BA4" s="98"/>
-      <c r="BB4" s="98"/>
-      <c r="BC4" s="98"/>
-      <c r="BD4" s="98"/>
-      <c r="BE4" s="99"/>
-      <c r="BF4" s="97">
+      <c r="AZ4" s="100"/>
+      <c r="BA4" s="100"/>
+      <c r="BB4" s="100"/>
+      <c r="BC4" s="100"/>
+      <c r="BD4" s="100"/>
+      <c r="BE4" s="101"/>
+      <c r="BF4" s="99">
         <f>BF5</f>
         <v>46265</v>
       </c>
-      <c r="BG4" s="98"/>
-      <c r="BH4" s="98"/>
-      <c r="BI4" s="98"/>
-      <c r="BJ4" s="98"/>
-      <c r="BK4" s="98"/>
-      <c r="BL4" s="99"/>
+      <c r="BG4" s="100"/>
+      <c r="BH4" s="100"/>
+      <c r="BI4" s="100"/>
+      <c r="BJ4" s="100"/>
+      <c r="BK4" s="100"/>
+      <c r="BL4" s="101"/>
     </row>
     <row r="5" spans="1:64" ht="15" customHeight="1">
       <c r="A5" s="9" t="s">
@@ -3129,7 +3129,7 @@
         <v>63</v>
       </c>
       <c r="D10" s="41">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E10" s="82">
         <v>46230</v>
@@ -3208,7 +3208,7 @@
         <v>62</v>
       </c>
       <c r="D11" s="41">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="E11" s="82">
         <f>F10</f>
@@ -3288,7 +3288,7 @@
         <v>64</v>
       </c>
       <c r="D12" s="41">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E12" s="82">
         <v>46235</v>
@@ -5532,17 +5532,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
   </mergeCells>
   <phoneticPr fontId="29"/>
   <conditionalFormatting sqref="D7:D41">
@@ -5722,23 +5722,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6030,22 +6019,29 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5144944C-1F1D-4162-962A-96F3FC8455D8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6072,9 +6068,13 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5144944C-1F1D-4162-962A-96F3FC8455D8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>